--- a/results/llama3_2_latest__gatefix/comparison_SelfCorrectionRAG/SelfCorrectionRAG_evaluated.xlsx
+++ b/results/llama3_2_latest__gatefix/comparison_SelfCorrectionRAG/SelfCorrectionRAG_evaluated.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -505,35 +505,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.01010100960871342</v>
+        <v>0.1651376098416708</v>
       </c>
       <c r="D2" t="n">
-        <v>7.188271943170174e-260</v>
+        <v>0.01890362647341236</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3537169694900513</v>
+        <v>0.6061280369758606</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.694999999999993</v>
+        <v>11.17238372093027</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07379375591296121</v>
+        <v>0.8107852412488175</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
       <c r="K2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.25</v>
+        <v>0.2795698924731183</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="3">
@@ -546,35 +548,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.0983606529965064</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>9.039352811507815e-232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4298741221427917</v>
+        <v>0.5689552426338196</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.694999999999993</v>
+        <v>33.14685897435899</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7155963302752294</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
       <c r="K3" t="n">
-        <v>0.38</v>
+        <v>0.045</v>
       </c>
       <c r="L3" t="n">
-        <v>0.25</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2105263157894737</v>
       </c>
     </row>
     <row r="4">
@@ -587,35 +591,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.2211538424038462</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1.734430471313534e-80</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2991204261779785</v>
+        <v>0.6441602110862732</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.694999999999993</v>
+        <v>54.93275</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.3472222222222222</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2045454545454545</v>
       </c>
     </row>
     <row r="5">
@@ -628,19 +634,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.0517241367215369</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1.691240673366888e-244</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2943938076496124</v>
+        <v>0.406010240316391</v>
       </c>
       <c r="F5" t="n">
-        <v>-6.694999999999993</v>
+        <v>18.74250000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06382978723404255</v>
+        <v>0.1178396072013093</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -648,15 +654,17 @@
       <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1176470588235294</v>
       </c>
     </row>
     <row r="6">
@@ -669,19 +677,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01273885288652687</v>
+        <v>0.09523809351473926</v>
       </c>
       <c r="D6" t="n">
-        <v>7.842246496009318e-255</v>
+        <v>1.724007354605445e-238</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3298570215702057</v>
+        <v>0.4076820313930511</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.694999999999993</v>
+        <v>40.09</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0896551724137931</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -689,15 +697,17 @@
       <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="7">
@@ -710,35 +720,37 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.004032257864935623</v>
+        <v>0.1007462671185815</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3.015350835165496e-79</v>
       </c>
       <c r="E7" t="n">
-        <v>0.353213906288147</v>
+        <v>0.5569169521331787</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.694999999999993</v>
+        <v>11.85032253947148</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02269421006691882</v>
+        <v>0.2173407041024149</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2</v>
+        <v>0.4560943643512451</v>
       </c>
     </row>
     <row r="8">
@@ -751,35 +763,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.08835341211012726</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2.796173118931514e-164</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3415371477603912</v>
+        <v>0.5113056302070618</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.694999999999993</v>
+        <v>47.43431818181818</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05416666666666667</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="9">
@@ -792,19 +806,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.006993006649469429</v>
+        <v>0.1609907098118452</v>
       </c>
       <c r="D9" t="n">
-        <v>4.626996437597695e-283</v>
+        <v>1.050480840321343e-159</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3237474858760834</v>
+        <v>0.6321372389793396</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.694999999999993</v>
+        <v>76.27844155844159</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04519119351100811</v>
+        <v>0.1622247972190035</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -812,15 +826,17 @@
       <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
       <c r="K9" t="n">
         <v>0.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1578947368421053</v>
       </c>
     </row>
     <row r="10">
@@ -833,35 +849,37 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.1533333300935556</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.0009558604485990607</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3335631489753723</v>
+        <v>0.5622940063476562</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.694999999999993</v>
+        <v>55.06017657192078</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05158730158730158</v>
+        <v>0.2645502645502645</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
       <c r="K10" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L10" t="n">
-        <v>0.25</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2352941176470588</v>
       </c>
     </row>
     <row r="11">
@@ -874,35 +892,37 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.006756756424625656</v>
+        <v>0.1137724528464628</v>
       </c>
       <c r="D11" t="n">
-        <v>3.199290466293744e-295</v>
+        <v>4.817247629422568e-161</v>
       </c>
       <c r="E11" t="n">
-        <v>0.312595933675766</v>
+        <v>0.6700990796089172</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.694999999999993</v>
+        <v>51.24500000000003</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04264625478403499</v>
+        <v>0.1623838162930563</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -915,19 +935,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.1230769207358107</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1.968548384043637e-159</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3295387625694275</v>
+        <v>0.5097022652626038</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.694999999999993</v>
+        <v>64.28885057471265</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04441913439635535</v>
+        <v>0.1503416856492027</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -935,15 +955,17 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="13">
@@ -956,35 +978,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.006644517945718055</v>
+        <v>0.08668730496947161</v>
       </c>
       <c r="D13" t="n">
-        <v>1.737745674680046e-291</v>
+        <v>2.573767504571472e-165</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3309608399868011</v>
+        <v>0.6250803470611572</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.694999999999993</v>
+        <v>72.83000000000003</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04323725055432372</v>
+        <v>0.1036585365853658</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="14">
@@ -997,35 +1021,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.1144578291152563</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>5.033313304015413e-160</v>
       </c>
       <c r="E14" t="n">
-        <v>0.327696293592453</v>
+        <v>0.5496810078620911</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.694999999999993</v>
+        <v>59.57166666666666</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04333333333333333</v>
+        <v>0.1538888888888889</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
       <c r="K14" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L14" t="n">
-        <v>0.25</v>
+        <v>0.4411764705882353</v>
       </c>
       <c r="M14" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1176470588235294</v>
       </c>
     </row>
     <row r="15">
@@ -1038,35 +1064,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.2658227801634354</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2.778062000719693e-155</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3345783352851868</v>
+        <v>0.6809143424034119</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.694999999999993</v>
+        <v>58.71729813664598</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1569416498993964</v>
+        <v>0.7183098591549296</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.25</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="M15" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="16">
@@ -1079,35 +1107,37 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.2511627858976745</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.08135740764894293</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3279084861278534</v>
+        <v>0.6782683730125427</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.694999999999993</v>
+        <v>67.17797468354433</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1112696148359486</v>
+        <v>0.8473609129814551</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.349112426035503</v>
       </c>
     </row>
     <row r="17">
@@ -1120,35 +1150,37 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.276923072662722</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>8.87895296788668e-156</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3277542293071747</v>
+        <v>0.6541492938995361</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.694999999999993</v>
+        <v>61.6818376623377</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1048387096774194</v>
+        <v>0.4973118279569892</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0.25</v>
+        <v>0.3877551020408163</v>
       </c>
       <c r="M17" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1538461538461539</v>
       </c>
     </row>
     <row r="18">
@@ -1161,35 +1193,37 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.24439918224016</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.01071388490788548</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3615763187408447</v>
+        <v>0.6431419253349304</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.694999999999993</v>
+        <v>57.83949565217392</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03037383177570093</v>
+        <v>0.2289719626168224</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3396226415094339</v>
       </c>
     </row>
     <row r="19">
@@ -1202,19 +1236,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.05511810955266911</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>8.672949743567673e-171</v>
       </c>
       <c r="E19" t="n">
-        <v>0.33333620429039</v>
+        <v>0.5145386457443237</v>
       </c>
       <c r="F19" t="n">
-        <v>-6.694999999999993</v>
+        <v>38.94119047619049</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05141727092946605</v>
+        <v>0.07119314436387607</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1222,15 +1256,17 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1095890410958904</v>
       </c>
     </row>
     <row r="20">
@@ -1243,35 +1279,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.008032128120514206</v>
+        <v>0.1379310318135553</v>
       </c>
       <c r="D20" t="n">
-        <v>1.21304235279905e-268</v>
+        <v>1.397268656437835e-80</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3513511121273041</v>
+        <v>0.5976909995079041</v>
       </c>
       <c r="F20" t="n">
-        <v>-6.694999999999993</v>
+        <v>53.29755255255256</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05535841022001419</v>
+        <v>0.2306600425833925</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L20" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.1823899371069182</v>
       </c>
     </row>
     <row r="21">
@@ -1284,35 +1322,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.1734417302108534</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>6.307314793855258e-79</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3501014113426208</v>
+        <v>0.5835224390029907</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.694999999999993</v>
+        <v>43.42000000000002</v>
       </c>
       <c r="G21" t="n">
-        <v>0.04419263456090652</v>
+        <v>0.4464589235127479</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.375</v>
+      </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L21" t="n">
-        <v>0.25</v>
+        <v>0.51</v>
       </c>
       <c r="M21" t="n">
-        <v>0.01408450704225352</v>
+        <v>0.2909090909090909</v>
       </c>
     </row>
     <row r="22">
@@ -1325,35 +1365,37 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.2941176420843338</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.03063005414254655</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3600354492664337</v>
+        <v>0.6253650188446045</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.694999999999993</v>
+        <v>35.56131779100531</v>
       </c>
       <c r="G22" t="n">
-        <v>0.04727272727272727</v>
+        <v>1.073333333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="M22" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="23">
@@ -1366,35 +1408,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.005847952928251443</v>
+        <v>0.08719345898922705</v>
       </c>
       <c r="D23" t="n">
-        <v>1.811128572821972e-307</v>
+        <v>8.424760656613393e-13</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3535859286785126</v>
+        <v>0.5638859272003174</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.694999999999993</v>
+        <v>20.78005882352943</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0358291226458429</v>
+        <v>0.112540192926045</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
       <c r="K23" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.25</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1346153846153846</v>
       </c>
     </row>
     <row r="24">
@@ -1407,19 +1451,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.1746031717208365</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>3.609335106029891e-158</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3177126049995422</v>
+        <v>0.495968759059906</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.694999999999993</v>
+        <v>77.67072463768118</v>
       </c>
       <c r="G24" t="n">
-        <v>0.119815668202765</v>
+        <v>0.2365591397849462</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1427,12 +1471,14 @@
       <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L24" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0.09090909090909091</v>
@@ -1448,35 +1494,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.2013422782144949</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1.058797756759345e-155</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3314136564731598</v>
+        <v>0.5474245548248291</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.694999999999993</v>
+        <v>32.18078947368423</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.3785822021116139</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="26">
@@ -1489,19 +1537,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.1428571402822066</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>5.42286353767171e-159</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3261704742908478</v>
+        <v>0.4237134456634521</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.694999999999993</v>
+        <v>24.03102941176473</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1351819757365685</v>
+        <v>0.2547660311958406</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1509,15 +1557,17 @@
       <c r="I26" t="n">
         <v>0</v>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
       <c r="K26" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="L26" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1025641025641026</v>
       </c>
     </row>
     <row r="27">
@@ -1530,35 +1580,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.2359550520912764</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>6.325060334079257e-156</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3252985775470734</v>
+        <v>0.5793122053146362</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.694999999999993</v>
+        <v>44.25500000000002</v>
       </c>
       <c r="G27" t="n">
-        <v>0.106703146374829</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1891891891891892</v>
       </c>
     </row>
     <row r="28">
@@ -1571,35 +1623,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.1923076883144314</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>2.438031653153288e-156</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3308320045471191</v>
+        <v>0.5616746544837952</v>
       </c>
       <c r="F28" t="n">
-        <v>-6.694999999999993</v>
+        <v>50.60811111111113</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1181818181818182</v>
+        <v>0.4212121212121212</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
       <c r="K28" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1954022988505747</v>
       </c>
     </row>
     <row r="29">
@@ -1612,35 +1666,37 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.1391304319092628</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2.249050944985316e-158</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3268276154994965</v>
+        <v>0.4437164664268494</v>
       </c>
       <c r="F29" t="n">
-        <v>-6.694999999999993</v>
+        <v>43.55833333333334</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1354166666666667</v>
+        <v>0.2690972222222222</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
       <c r="K29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.05882352941176471</v>
       </c>
     </row>
     <row r="30">
@@ -1653,35 +1709,37 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.1351351329985391</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2.244535351910224e-155</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4468841254711151</v>
+        <v>0.4958815574645996</v>
       </c>
       <c r="F30" t="n">
-        <v>-6.694999999999993</v>
+        <v>45.98723076923079</v>
       </c>
       <c r="G30" t="n">
-        <v>0.78</v>
+        <v>3.68</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
       <c r="K30" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>0.25</v>
+        <v>0.4528301886792453</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1379310344827586</v>
       </c>
     </row>
     <row r="31">
@@ -1694,35 +1752,37 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.1194029827489419</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1.781009471778631e-155</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4375941157341003</v>
+        <v>0.4875025153160095</v>
       </c>
       <c r="F31" t="n">
-        <v>-6.694999999999993</v>
+        <v>49.3340305084746</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7572815533980582</v>
+        <v>4.368932038834951</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.25</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="M31" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.239766081871345</v>
       </c>
     </row>
     <row r="32">
@@ -1735,35 +1795,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.109589038934134</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>2.083664844636364e-155</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4345121085643768</v>
+        <v>0.4611914157867432</v>
       </c>
       <c r="F32" t="n">
-        <v>-6.694999999999993</v>
+        <v>43.80226495726498</v>
       </c>
       <c r="G32" t="n">
-        <v>0.78</v>
+        <v>4.04</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.186046511627907</v>
       </c>
     </row>
     <row r="33">
@@ -1776,35 +1838,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.331034478120333</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>5.556490054616226e-79</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4005701541900635</v>
+        <v>0.6410205960273743</v>
       </c>
       <c r="F33" t="n">
-        <v>-6.694999999999993</v>
+        <v>70.02869718309861</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2160664819944598</v>
+        <v>1.861495844875346</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
       <c r="K33" t="n">
         <v>0.5</v>
       </c>
       <c r="L33" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.4857142857142858</v>
       </c>
     </row>
     <row r="34">
@@ -1817,35 +1881,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.233333328817284</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>2.407401295684917e-155</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3832495212554932</v>
+        <v>0.6021385788917542</v>
       </c>
       <c r="F34" t="n">
-        <v>-6.694999999999993</v>
+        <v>56.239717920354</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1133720930232558</v>
+        <v>0.625</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
       <c r="K34" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2307692307692308</v>
       </c>
     </row>
     <row r="35">
@@ -1858,35 +1924,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.2721088391630803</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.03134301059563741</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3523319959640503</v>
+        <v>0.6418632864952087</v>
       </c>
       <c r="F35" t="n">
-        <v>-6.694999999999993</v>
+        <v>25.04384615384615</v>
       </c>
       <c r="G35" t="n">
-        <v>0.06830122591943957</v>
+        <v>0.4649737302977233</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5</v>
+        <v>0.6212121212121212</v>
       </c>
       <c r="M35" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3121693121693122</v>
       </c>
     </row>
     <row r="36">
@@ -1899,35 +1967,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.1851851812856272</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.08901085364869357</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3204767107963562</v>
+        <v>0.7136691808700562</v>
       </c>
       <c r="F36" t="n">
-        <v>-6.694999999999993</v>
+        <v>16.084657480315</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1236133122028526</v>
+        <v>0.4659270998415214</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
       <c r="K36" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="L36" t="n">
-        <v>0.25</v>
+        <v>0.696969696969697</v>
       </c>
       <c r="M36" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2366412213740458</v>
       </c>
     </row>
     <row r="37">
@@ -1940,35 +2010,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.1254901913282586</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>5.292344692655624e-232</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3582548201084137</v>
+        <v>0.5988379120826721</v>
       </c>
       <c r="F37" t="n">
-        <v>-6.694999999999993</v>
+        <v>81.12424089068827</v>
       </c>
       <c r="G37" t="n">
-        <v>0.08271474019088017</v>
+        <v>0.6436903499469777</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
       <c r="K37" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L37" t="n">
-        <v>0.25</v>
+        <v>0.4714285714285714</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.4039735099337748</v>
       </c>
     </row>
     <row r="38">
@@ -1981,35 +2053,37 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.2626262580553005</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.03216663672496465</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3565259277820587</v>
+        <v>0.5355229377746582</v>
       </c>
       <c r="F38" t="n">
-        <v>-6.694999999999993</v>
+        <v>36.9065384615385</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1009055627425614</v>
+        <v>0.5963777490297542</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
       <c r="K38" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1946308724832215</v>
       </c>
     </row>
     <row r="39">
@@ -2022,19 +2096,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.1944444408371914</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>5.019806190416597e-233</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3533079922199249</v>
+        <v>0.5569300055503845</v>
       </c>
       <c r="F39" t="n">
-        <v>-6.694999999999993</v>
+        <v>62.34923076923079</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1150442477876106</v>
+        <v>0.336283185840708</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2042,15 +2116,17 @@
       <c r="I39" t="n">
         <v>0</v>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L39" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.07514450867052024</v>
       </c>
     </row>
     <row r="40">
@@ -2063,35 +2139,37 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.1111111086395062</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>3.31009421283509e-157</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2973054349422455</v>
+        <v>0.6540348529815674</v>
       </c>
       <c r="F40" t="n">
-        <v>-6.694999999999993</v>
+        <v>49.74600358422941</v>
       </c>
       <c r="G40" t="n">
-        <v>0.08590308370044053</v>
+        <v>0.25</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
       <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
         <v>0.5</v>
       </c>
-      <c r="L40" t="n">
-        <v>0.25</v>
-      </c>
       <c r="M40" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2307692307692308</v>
       </c>
     </row>
     <row r="41">
@@ -2104,35 +2182,37 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.1151079120915067</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>2.503385863140841e-85</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2983242273330688</v>
+        <v>0.625676691532135</v>
       </c>
       <c r="F41" t="n">
-        <v>-6.694999999999993</v>
+        <v>61.69963636363636</v>
       </c>
       <c r="G41" t="n">
-        <v>0.05349794238683128</v>
+        <v>0.139917695473251</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L41" t="n">
-        <v>0.25</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="42">
@@ -2145,35 +2225,37 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01273885288652687</v>
+        <v>0.1005586566561594</v>
       </c>
       <c r="D42" t="n">
-        <v>7.842246496009318e-255</v>
+        <v>1.22342463423494e-234</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3304620385169983</v>
+        <v>0.5203850269317627</v>
       </c>
       <c r="F42" t="n">
-        <v>-6.694999999999993</v>
+        <v>46.14681818181819</v>
       </c>
       <c r="G42" t="n">
-        <v>0.08914285714285715</v>
+        <v>0.2434285714285714</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L42" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="43">
@@ -2186,35 +2268,37 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.2468354380668163</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>4.012739307999906e-155</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3637755811214447</v>
+        <v>0.6392710208892822</v>
       </c>
       <c r="F43" t="n">
-        <v>-6.694999999999993</v>
+        <v>48.21031732418527</v>
       </c>
       <c r="G43" t="n">
-        <v>0.07228915662650602</v>
+        <v>0.9351251158480074</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
       <c r="K43" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.02564102564102564</v>
+        <v>0.4160583941605839</v>
       </c>
     </row>
     <row r="44">
@@ -2227,35 +2311,37 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.1415929164127967</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>6.709237460203354e-79</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3320682942867279</v>
+        <v>0.6393852829933167</v>
       </c>
       <c r="F44" t="n">
-        <v>-6.694999999999993</v>
+        <v>-7.318215384615371</v>
       </c>
       <c r="G44" t="n">
-        <v>0.08955223880597014</v>
+        <v>0.5304247990815155</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0.25</v>
+        <v>0.3859649122807017</v>
       </c>
       <c r="M44" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3311036789297659</v>
       </c>
     </row>
     <row r="45">
@@ -2268,35 +2354,37 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.3083700403510429</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>0.03261355567381161</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3620854616165161</v>
+        <v>0.6349319219589233</v>
       </c>
       <c r="F45" t="n">
-        <v>-6.694999999999993</v>
+        <v>49.43543628808865</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02138744173293118</v>
+        <v>0.3745544282972306</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
       <c r="K45" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.6604938271604939</v>
       </c>
     </row>
     <row r="46">
@@ -2309,35 +2397,37 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.2337278075443787</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>0.01484983994858796</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3481395244598389</v>
+        <v>0.6115736365318298</v>
       </c>
       <c r="F46" t="n">
-        <v>-6.694999999999993</v>
+        <v>56.87479856015509</v>
       </c>
       <c r="G46" t="n">
-        <v>0.02160066463583495</v>
+        <v>0.2650235391858211</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
       <c r="K46" t="n">
         <v>0.5</v>
       </c>
       <c r="L46" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.5294117647058824</v>
       </c>
     </row>
     <row r="47">
@@ -2350,35 +2440,37 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.2773109211246558</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>0.001247994874258283</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3639097213745117</v>
+        <v>0.6308389902114868</v>
       </c>
       <c r="F47" t="n">
-        <v>-6.694999999999993</v>
+        <v>21.57368421052632</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0310880829015544</v>
+        <v>0.2351534475886808</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
       <c r="K47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.2792792792792793</v>
       </c>
     </row>
     <row r="48">
@@ -2391,35 +2483,37 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.2115384576035503</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1.650703816886613e-155</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3680242300033569</v>
+        <v>0.5837224125862122</v>
       </c>
       <c r="F48" t="n">
-        <v>-6.694999999999993</v>
+        <v>40.48416666666668</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1670235546038544</v>
+        <v>0.5053533190578159</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
       <c r="K48" t="n">
         <v>0.5</v>
       </c>
       <c r="L48" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2452830188679246</v>
       </c>
     </row>
     <row r="49">
@@ -2432,35 +2526,37 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.1523809496671202</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>2.943114372540767e-79</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3522202372550964</v>
+        <v>0.5638047456741333</v>
       </c>
       <c r="F49" t="n">
-        <v>-6.694999999999993</v>
+        <v>73.89631578947372</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1502890173410405</v>
+        <v>0.3429672447013488</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L49" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1869918699186992</v>
       </c>
     </row>
     <row r="50">
@@ -2473,35 +2569,37 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.1911764660207614</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>0.03147446394118519</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3514077365398407</v>
+        <v>0.5948474407196045</v>
       </c>
       <c r="F50" t="n">
-        <v>-6.694999999999993</v>
+        <v>62.39579243765084</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1494252873563219</v>
+        <v>0.6609195402298851</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
       <c r="K50" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2805755395683453</v>
       </c>
     </row>
     <row r="51">
@@ -2514,35 +2612,37 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.1585365816158537</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1.264024049723077e-155</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3513664901256561</v>
+        <v>0.5793190002441406</v>
       </c>
       <c r="F51" t="n">
-        <v>-6.694999999999993</v>
+        <v>11.9230913978495</v>
       </c>
       <c r="G51" t="n">
-        <v>0.103861517976032</v>
+        <v>0.4167776298268975</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>0.25</v>
+        <v>0.3823529411764706</v>
       </c>
       <c r="M51" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.3710691823899371</v>
       </c>
     </row>
     <row r="52">
@@ -2555,35 +2655,37 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.008403360933196829</v>
+        <v>0.2078651640166962</v>
       </c>
       <c r="D52" t="n">
-        <v>2.960553565183628e-265</v>
+        <v>3.811146423519126e-155</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3619620203971863</v>
+        <v>0.5970848798751831</v>
       </c>
       <c r="F52" t="n">
-        <v>-6.694999999999993</v>
+        <v>46.06334848484849</v>
       </c>
       <c r="G52" t="n">
-        <v>0.05656272661348803</v>
+        <v>0.5351704133430022</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
       <c r="K52" t="n">
-        <v>0.75</v>
+        <v>0.87</v>
       </c>
       <c r="L52" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.5024875621890548</v>
       </c>
     </row>
     <row r="53">
@@ -2596,35 +2698,37 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.1415384596650414</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>8.700512584883141e-05</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3393140435218811</v>
+        <v>0.6485660076141357</v>
       </c>
       <c r="F53" t="n">
-        <v>-6.694999999999993</v>
+        <v>41.75385167464117</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0416221985058698</v>
+        <v>0.1339381003201708</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
       <c r="K53" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.1121495327102804</v>
       </c>
     </row>
     <row r="54">
@@ -2637,35 +2741,37 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.1744966400792758</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>5.120040658383118e-80</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3256970345973969</v>
+        <v>0.6241183876991272</v>
       </c>
       <c r="F54" t="n">
-        <v>-6.694999999999993</v>
+        <v>-9.829369565217377</v>
       </c>
       <c r="G54" t="n">
-        <v>0.05739514348785872</v>
+        <v>0.4753495217071376</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2763157894736842</v>
       </c>
     </row>
     <row r="55">
@@ -2678,35 +2784,37 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.1865671620196592</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>2.356233700818133e-06</v>
       </c>
       <c r="E55" t="n">
-        <v>0.343548446893692</v>
+        <v>0.6216738820075989</v>
       </c>
       <c r="F55" t="n">
-        <v>-6.694999999999993</v>
+        <v>24.22750000000002</v>
       </c>
       <c r="G55" t="n">
-        <v>0.05045278137128072</v>
+        <v>0.1552393272962484</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
       <c r="K55" t="n">
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1397849462365592</v>
       </c>
     </row>
     <row r="56">
@@ -2719,35 +2827,37 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>0.1447368390997231</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>5.328094693801895e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>0.3342143893241882</v>
+        <v>0.5665460824966431</v>
       </c>
       <c r="F56" t="n">
-        <v>-6.694999999999993</v>
+        <v>39.12070850202431</v>
       </c>
       <c r="G56" t="n">
-        <v>0.04977664326738992</v>
+        <v>0.2335673261008296</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L56" t="n">
-        <v>0.25</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1935483870967742</v>
       </c>
     </row>
     <row r="57">
@@ -2760,35 +2870,37 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>0.2269503513844877</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>0.007178738932603332</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3695140182971954</v>
+        <v>0.5896973609924316</v>
       </c>
       <c r="F57" t="n">
-        <v>-6.694999999999993</v>
+        <v>52.94386093461776</v>
       </c>
       <c r="G57" t="n">
-        <v>0.02687801516195727</v>
+        <v>0.2639558924879393</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
       <c r="K57" t="n">
         <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.04</v>
+        <v>0.2913385826771653</v>
       </c>
     </row>
     <row r="58">
@@ -2801,35 +2913,37 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.0120481921868196</v>
+        <v>0.2145593822462971</v>
       </c>
       <c r="D58" t="n">
-        <v>3.542014107114671e-257</v>
+        <v>3.760073892041286e-155</v>
       </c>
       <c r="E58" t="n">
-        <v>0.3487640619277954</v>
+        <v>0.6613680124282837</v>
       </c>
       <c r="F58" t="n">
-        <v>-6.694999999999993</v>
+        <v>47.53226005513096</v>
       </c>
       <c r="G58" t="n">
-        <v>0.08423326133909287</v>
+        <v>0.6987041036717062</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
       <c r="K58" t="n">
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>0.25</v>
+        <v>0.475609756097561</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.4047619047619048</v>
       </c>
     </row>
     <row r="59">
@@ -2842,35 +2956,37 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>0.315789468690849</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>7.549254288381402e-79</v>
       </c>
       <c r="E59" t="n">
-        <v>0.359289288520813</v>
+        <v>0.6473841071128845</v>
       </c>
       <c r="F59" t="n">
-        <v>-6.694999999999993</v>
+        <v>37.85146137677353</v>
       </c>
       <c r="G59" t="n">
-        <v>0.09848484848484848</v>
+        <v>1.136363636363636</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.6296296296296295</v>
       </c>
     </row>
     <row r="60">
@@ -2883,35 +2999,37 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.00446428549356267</v>
+        <v>0.1285140542600119</v>
       </c>
       <c r="D60" t="n">
-        <v>8.265132997605698e-314</v>
+        <v>1.889803135917405e-158</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3573783934116364</v>
+        <v>0.5116021633148193</v>
       </c>
       <c r="F60" t="n">
-        <v>-6.694999999999993</v>
+        <v>12.21455188679249</v>
       </c>
       <c r="G60" t="n">
-        <v>0.02725366876310273</v>
+        <v>0.129979035639413</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1970802919708029</v>
       </c>
     </row>
     <row r="61">
@@ -2924,35 +3042,37 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>0.2499999959781805</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>7.751579743209176e-79</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3793801069259644</v>
+        <v>0.5810978412628174</v>
       </c>
       <c r="F61" t="n">
-        <v>-6.694999999999993</v>
+        <v>40.87333333333336</v>
       </c>
       <c r="G61" t="n">
-        <v>0.3157894736842105</v>
+        <v>2.214574898785425</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
       <c r="K61" t="n">
         <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.4146341463414633</v>
       </c>
     </row>
     <row r="62">
@@ -2965,35 +3085,37 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>0.1666666630230035</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>1.82771932340829e-156</v>
       </c>
       <c r="E62" t="n">
-        <v>0.3254241049289703</v>
+        <v>0.4752743244171143</v>
       </c>
       <c r="F62" t="n">
-        <v>-6.694999999999993</v>
+        <v>48.63550000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>0.195</v>
+        <v>0.4275</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
       <c r="K62" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07407407407407407</v>
       </c>
     </row>
     <row r="63">
@@ -3006,19 +3128,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>0.06896551572318671</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>2.291493039758307e-239</v>
       </c>
       <c r="E63" t="n">
-        <v>0.3176030814647675</v>
+        <v>0.4284061789512634</v>
       </c>
       <c r="F63" t="n">
-        <v>-6.694999999999993</v>
+        <v>50.56057692307695</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1087866108786611</v>
+        <v>0.1743375174337518</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3026,15 +3148,17 @@
       <c r="I63" t="n">
         <v>0</v>
       </c>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
       <c r="K63" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07216494845360824</v>
       </c>
     </row>
     <row r="64">
@@ -3047,35 +3171,37 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>0.181818178267886</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1.027963793723237e-155</v>
       </c>
       <c r="E64" t="n">
-        <v>0.3184672594070435</v>
+        <v>0.5958529114723206</v>
       </c>
       <c r="F64" t="n">
-        <v>-6.694999999999993</v>
+        <v>45.57954545454547</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1278688524590164</v>
+        <v>0.4377049180327869</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0.25</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="M64" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2215568862275449</v>
       </c>
     </row>
     <row r="65">
@@ -3088,35 +3214,37 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>0.1592920326008302</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>1.644973154223386e-157</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3219119608402252</v>
+        <v>0.4853648841381073</v>
       </c>
       <c r="F65" t="n">
-        <v>-6.694999999999993</v>
+        <v>56.70000000000002</v>
       </c>
       <c r="G65" t="n">
-        <v>0.156312625250501</v>
+        <v>0.2985971943887776</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1025641025641026</v>
       </c>
     </row>
     <row r="66">
@@ -3129,35 +3257,37 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>0.1925133656827476</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>3.687106795403599e-156</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3294911682605743</v>
+        <v>0.5733634829521179</v>
       </c>
       <c r="F66" t="n">
-        <v>-6.694999999999993</v>
+        <v>38.49889423076925</v>
       </c>
       <c r="G66" t="n">
-        <v>0.09786700125470514</v>
+        <v>0.4015056461731493</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L66" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2763157894736842</v>
       </c>
     </row>
     <row r="67">
@@ -3170,35 +3300,37 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>0.2547169763474547</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>9.511776100514363e-79</v>
       </c>
       <c r="E67" t="n">
-        <v>0.3287849128246307</v>
+        <v>0.6278840303421021</v>
       </c>
       <c r="F67" t="n">
-        <v>-6.694999999999993</v>
+        <v>65.05757466281314</v>
       </c>
       <c r="G67" t="n">
-        <v>0.1068493150684932</v>
+        <v>0.7</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
       <c r="K67" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2233009708737864</v>
       </c>
     </row>
     <row r="68">
@@ -3211,35 +3343,37 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>0.1333333308843538</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1.857009361188231e-155</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4152870178222656</v>
+        <v>0.4196167886257172</v>
       </c>
       <c r="F68" t="n">
-        <v>-6.694999999999993</v>
+        <v>-1.215963600909959</v>
       </c>
       <c r="G68" t="n">
-        <v>0.6141732283464567</v>
+        <v>5.125984251968504</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
       <c r="K68" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0.2</v>
+        <v>0.2553191489361702</v>
       </c>
     </row>
   </sheetData>
